--- a/output/pdf_financials_xlsx/TRV.P.xlsx
+++ b/output/pdf_financials_xlsx/TRV.P.xlsx
@@ -484,30 +484,20 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -516,30 +506,20 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -548,30 +528,20 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,30 +550,20 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.019767</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -612,30 +572,20 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -644,30 +594,20 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -676,30 +616,20 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.019767</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-0.047916</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>-0.043902</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -708,30 +638,20 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.019767</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.047916</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.043902</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -740,30 +660,20 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -772,30 +682,20 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -804,30 +704,20 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -836,30 +726,20 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -868,30 +748,20 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.112022</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.047916</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.038876</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.024181</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.038216</v>
       </c>
     </row>
     <row r="17">
@@ -900,30 +770,20 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -996,30 +856,20 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.112022</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.047916</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.038876</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.024181</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-0.038216</v>
       </c>
     </row>
     <row r="21">
@@ -1028,30 +878,20 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1060,30 +900,20 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1093,7 +923,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-0.047916</v>
+        <v>-0.112022</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.047916</v>
@@ -1136,30 +966,20 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1200,30 +1020,20 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.112022</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.047916</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.038876</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.024181</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-0.038216</v>
       </c>
     </row>
     <row r="28">
@@ -1232,30 +1042,20 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1264,30 +1064,20 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.112022</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.047916</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.038876</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.024181</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-0.038216</v>
       </c>
     </row>
     <row r="30">
@@ -1328,30 +1118,20 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1399,30 +1179,20 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1431,30 +1201,20 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1463,30 +1223,20 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1495,30 +1245,20 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1527,30 +1267,20 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1559,30 +1289,20 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1591,30 +1311,20 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1623,30 +1333,20 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1655,30 +1355,20 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1687,30 +1377,20 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1719,30 +1399,20 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1751,30 +1421,20 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1783,30 +1443,20 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1815,30 +1465,20 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1847,30 +1487,20 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1911,30 +1541,20 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1943,30 +1563,20 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1975,30 +1585,20 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2007,30 +1607,20 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2039,30 +1629,20 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2103,30 +1683,20 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2135,30 +1705,20 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2167,30 +1727,20 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2199,30 +1749,20 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2231,30 +1771,20 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2263,30 +1793,20 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2349,30 +1869,20 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2381,30 +1891,20 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2413,30 +1913,20 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2445,30 +1935,20 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2499,30 +1979,20 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2531,30 +2001,20 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2563,30 +2023,20 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2595,30 +2045,20 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2627,30 +2067,20 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2659,30 +2089,20 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2691,30 +2111,20 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2755,30 +2165,20 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2787,30 +2187,20 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2819,30 +2209,20 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2883,30 +2263,20 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2915,30 +2285,20 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2947,30 +2307,20 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2979,30 +2329,20 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3011,30 +2351,20 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3097,30 +2427,20 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.524573</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.524573</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.524573</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.524573</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.524573</v>
       </c>
     </row>
     <row r="89">
@@ -3129,30 +2449,20 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -3183,30 +2493,20 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -3237,30 +2537,20 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -3291,30 +2581,20 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3323,30 +2603,20 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.521504</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0.473588</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.434712</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.410531</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.372315</v>
       </c>
     </row>
     <row r="97">
@@ -3384,30 +2654,20 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.112022</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.047916</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.038876</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.024181</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-0.038216</v>
       </c>
     </row>
     <row r="100">
@@ -3416,30 +2676,20 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -3448,30 +2698,20 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3480,30 +2720,20 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3512,30 +2742,20 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.000334</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>-0.000156</v>
       </c>
     </row>
     <row r="104">
@@ -3545,7 +2765,7 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>0.008018000000000001</v>
+        <v>0.058597</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.017757</v>
@@ -3566,30 +2786,20 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3598,30 +2808,20 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.032399</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.030159</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.044907</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.015486</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>-0.06732299999999999</v>
       </c>
     </row>
     <row r="107">
@@ -3633,25 +2833,17 @@
       <c r="B107" s="3" t="n">
         <v>0.071605</v>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3660,30 +2852,20 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3692,30 +2874,20 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3724,30 +2896,20 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3756,30 +2918,20 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3788,30 +2940,20 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3820,30 +2962,20 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3852,30 +2984,20 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3884,30 +3006,20 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3916,30 +3028,20 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3948,30 +3050,20 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3980,30 +3072,20 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -4044,30 +3126,20 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -4076,30 +3148,20 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -4108,30 +3170,20 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -4140,30 +3192,20 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -4172,30 +3214,20 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -4204,30 +3236,20 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -4236,30 +3258,20 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -4300,30 +3312,20 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -4332,10 +3334,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.6125</v>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
@@ -4364,10 +3364,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.580101</v>
@@ -4388,30 +3386,20 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4420,30 +3408,20 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.580101</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.030159</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.044907</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.015486</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-0.06732299999999999</v>
       </c>
     </row>
     <row r="133">
@@ -4474,30 +3452,20 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -5167,7 +4135,11 @@
           <t>Net loss for the year $</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -5241,7 +4213,11 @@
           <t>Prepaids</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -5317,7 +4293,11 @@
           <t>Changes in non-cash working capital items total</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>-0.032399</v>
       </c>
@@ -5350,7 +4330,11 @@
           <t>Change in cash during the year</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -5502,7 +4486,11 @@
           <t>Net loss for the period $</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>-0.112022</v>
       </c>
@@ -5627,7 +4615,11 @@
           <t>Financing activities total</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.6125</v>
       </c>
@@ -5668,7 +4660,11 @@
           <t>Change in cash during the period</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.580101</v>
       </c>
@@ -6006,7 +5002,11 @@
           <t>Share issuance costs included in accounts payable $</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>0.050579</v>
       </c>
@@ -6680,7 +5680,11 @@
           <t>Operating expenses total</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -6801,7 +5805,11 @@
           <t>Net loss and comprehensive loss for the period $</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>-0.112022</v>
       </c>
@@ -7129,7 +6137,11 @@
           <t>Net loss for the period - - -</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>-0.112022</v>
       </c>
@@ -7207,7 +6219,11 @@
           <t>Filing fees</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
         <v>0.019767</v>
       </c>
@@ -7289,7 +6305,11 @@
           <t>Net loss and comprehensive loss for the period $</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>-0.112022</v>
       </c>

--- a/output/pdf_financials_xlsx/TRV.P.xlsx
+++ b/output/pdf_financials_xlsx/TRV.P.xlsx
@@ -431,6 +431,14 @@
   </sheetPr>
   <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/TRV.P.xlsx
+++ b/output/pdf_financials_xlsx/TRV.P.xlsx
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.071862</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.010227</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.006297</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.006886</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.005397</v>
       </c>
     </row>
     <row r="10">
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.019767</v>
+        <v>0.091629</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-0.047916</v>
+        <v>0.047916</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.043902</v>
+        <v>0.043902</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.006886</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.005397</v>
       </c>
     </row>
     <row r="11">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.019767</v>
+        <v>-0.091629</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.047916</v>
+        <v>-0.047916</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.043902</v>
+        <v>-0.043902</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.006886</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-0.005397</v>
       </c>
     </row>
     <row r="12">
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -779,19 +779,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -3519,7 +3519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3750,10 +3750,8 @@
           <t>TotalLiabilities</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="5" t="n">
+        <v>0.058597</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.07635400000000001</v>
@@ -4130,74 +4128,78 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>-0.047916</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>-0.038876</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>-0.024181</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>-0.038216</v>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GST recoverable</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities $</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.058597</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n">
-        <v>-5.2e-05</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>5.2e-05</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -4213,17 +4215,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prepaids</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4231,21 +4233,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F18" s="5" t="n">
+        <v>-0.047916</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.038876</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.000334</v>
+        <v>-0.024181</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.000156</v>
+        <v>-0.038216</v>
       </c>
     </row>
     <row r="19">
@@ -4261,28 +4259,30 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0.008018000000000001</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.017757</v>
+          <t>GST recoverable</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.005979</v>
+        <v>-5.2e-05</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.008977000000000001</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>-0.028951</v>
+        <v>5.2e-05</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -4298,28 +4298,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items total</t>
+          <t>Prepaids</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>-0.032399</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>-0.030159</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-0.044907</v>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.015486</v>
+        <v>-0.000334</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.06732299999999999</v>
+        <v>-0.000156</v>
       </c>
     </row>
     <row r="21">
@@ -4335,30 +4341,28 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.008018000000000001</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.030159</v>
+        <v>0.017757</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.044907</v>
+        <v>-0.005979</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.015486</v>
+        <v>0.008977000000000001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.06732299999999999</v>
+        <v>-0.028951</v>
       </c>
     </row>
     <row r="22">
@@ -4374,30 +4378,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Changes in non-cash working capital items total</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.032399</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.580101</v>
+        <v>-0.030159</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.549942</v>
+        <v>-0.044907</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.505035</v>
+        <v>-0.015486</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.489549</v>
+        <v>-0.06732299999999999</v>
       </c>
     </row>
     <row r="23">
@@ -4413,12 +4415,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Change in cash during the year</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4427,16 +4429,16 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.549942</v>
+        <v>-0.030159</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.505035</v>
+        <v>-0.044907</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.489549</v>
+        <v>-0.015486</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.422226</v>
+        <v>-0.06732299999999999</v>
       </c>
     </row>
     <row r="24">
@@ -4447,35 +4449,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ended incorporation on</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2022 December</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" s="5" t="n">
-        <v>0.002021</v>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.580101</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.549942</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.505035</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0.489549</v>
       </c>
     </row>
     <row r="25">
@@ -4486,39 +4488,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>-0.112022</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-0.047916</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.549942</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.505035</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.489549</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>0.422226</v>
       </c>
     </row>
     <row r="26">
@@ -4529,26 +4527,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>ended        incorporation on</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 4)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>2022 December</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="n">
-        <v>0.071605</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002021</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4574,22 +4566,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Share subscription net of issue costs</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
-        <v>0.6125</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.112022</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-0.047916</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4615,21 +4609,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Financing activities total</t>
+          <t>Share-based compensation (Note 4)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.6125</v>
+        <v>0.071605</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4665,19 +4659,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Change in cash during the period</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Share subscription net of issue costs</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" s="5" t="n">
-        <v>0.580101</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>-0.030159</v>
+        <v>0.6125</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4708,21 +4700,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Financing activities total</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0.580101</v>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4753,19 +4745,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
+          <t>Change in cash during the period</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
         <v>0.580101</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.549942</v>
+        <v>-0.030159</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4791,22 +4783,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fair value of broker warrants issued with IPO (note 4) $</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>0.037348</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.580101</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4832,24 +4828,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Share issuance costs included in accounts payable</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Share issuance costs included in accounts payable and accrued liabilities $</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.050579</v>
+        <v>0.580101</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.050579</v>
+        <v>0.549942</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4875,21 +4871,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 4)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Fair value of broker warrants issued with IPO (note 4) $</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
-        <v>0.071605</v>
+        <v>0.037348</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4920,22 +4912,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Share issuance costs included in accounts payable</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Share subscriptions net of issue costs (note 4)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Share issuance costs included in accounts payable and accrued liabilities $</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
-        <v>0.6125</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.050579</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.050579</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4961,17 +4955,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Non-cash financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fair value of broker warrants issued with IPO (note 4) $</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Share-based compensation (note 4)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
-        <v>0.037348</v>
+        <v>0.071605</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5002,21 +5000,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Non-cash financing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Share issuance costs included in accounts payable $</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Share subscriptions net of issue costs (note 4)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" s="5" t="n">
-        <v>0.050579</v>
+        <v>0.6125</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5042,67 +5036,87 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Non-cash financing activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Office $</t>
+          <t>Fair value of broker warrants issued with IPO (note 4) $</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>0.000257</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>0.000401</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.000527</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>0.000798</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>0.000661</v>
+        <v>0.037348</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Non-cash financing activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Filing and listing fees</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Share issuance costs included in accounts payable $</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
-        <v>0.019767</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.007887</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.007386</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>0.008621</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0.007371</v>
+        <v>0.050579</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -5113,33 +5127,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Corporate and administrative</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Corporate and administrative services (Note 7)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office $</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.000257</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.000401</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.016654</v>
+        <v>0.000527</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.012904</v>
+        <v>0.000798</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.014101</v>
+        <v>0.000661</v>
       </c>
     </row>
     <row r="41">
@@ -5150,37 +5164,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Corporate and administrative</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Filing and listing fees</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" s="5" t="n">
+        <v>0.019767</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.007887</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.013565</v>
+        <v>0.007386</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.017682</v>
+        <v>0.008621</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>0.022712</v>
+        <v>0.007371</v>
       </c>
     </row>
     <row r="42">
@@ -5196,7 +5202,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
+          <t>Corporate and administrative services (Note 7)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -5211,13 +5217,13 @@
         </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.00577</v>
+        <v>0.016654</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.006088</v>
+        <v>0.012904</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.004736</v>
+        <v>0.014101</v>
       </c>
     </row>
     <row r="43">
@@ -5233,10 +5239,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Corporate and administrative total</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5248,13 +5258,13 @@
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.043902</v>
+        <v>0.013565</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>-0.046093</v>
+        <v>0.017682</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>-0.049581</v>
+        <v>0.022712</v>
       </c>
     </row>
     <row r="44">
@@ -5265,17 +5275,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Corporate and administrative</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Transfer agent</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5289,13 +5299,13 @@
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.005026</v>
+        <v>0.00577</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.021912</v>
+        <v>0.006088</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0.011365</v>
+        <v>0.004736</v>
       </c>
     </row>
     <row r="45">
@@ -5306,35 +5316,33 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive</t>
+          <t>Corporate and administrative</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Corporate and administrative total</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>-0.047916</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.038876</v>
+        <v>-0.043902</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>-0.024181</v>
+        <v>-0.046093</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>-0.038216</v>
+        <v>-0.049581</v>
       </c>
     </row>
     <row r="46">
@@ -5345,33 +5353,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>-1e-08</v>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0</v>
+        <v>0.005026</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0</v>
+        <v>0.021912</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>0</v>
+        <v>0.011365</v>
       </c>
     </row>
     <row r="47">
@@ -5382,31 +5394,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>common shares outstanding –</t>
+          <t>Net loss and comprehensive</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>common shares outstanding – basic and diluted (Note 4)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>9</v>
+        <v>-0.047916</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>9</v>
+        <v>-0.038876</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>9</v>
+        <v>-0.024181</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>9</v>
+        <v>-0.038216</v>
       </c>
     </row>
     <row r="48">
@@ -5417,31 +5433,33 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Net loss and comprehensive</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 9,000,000 $ 524,573 $ 108,953 $</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.434712</v>
+        <v>-1e-08</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.434712</v>
+        <v>0</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.434712</v>
+        <v>0</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>-0.198814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5452,33 +5470,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>common shares outstanding –</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>-0.047916</v>
+          <t>common shares outstanding – basic and diluted (Note 4)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>-0.047916</v>
+        <v>9</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.038876</v>
+        <v>9</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>-0.024181</v>
+        <v>9</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>-0.024181</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -5494,7 +5510,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 9,000,000 $ 524,573 $ 108,953 $</t>
+          <t>Balance, December 31, 2023 9,000,000 $ 524,573 $ 108,953 $</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -5503,19 +5519,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F50" s="5" t="n">
+        <v>0.434712</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.410531</v>
+        <v>0.434712</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.410531</v>
+        <v>0.434712</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-0.222995</v>
+        <v>-0.198814</v>
       </c>
     </row>
     <row r="51">
@@ -5531,30 +5545,30 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2025 9,000,000 $ 524,573 $ 108,953 $</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F51" s="5" t="n">
+        <v>-0.047916</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.038876</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.372315</v>
+        <v>-0.024181</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>-0.261211</v>
+        <v>-0.024181</v>
       </c>
     </row>
     <row r="52">
@@ -5570,26 +5584,28 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 9,000,000 $ 524,573 $ 108,953 $</t>
+          <t>Balance, December 31, 2024 9,000,000 $ 524,573 $ 108,953 $</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>0.473588</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>0.473588</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.473588</v>
+        <v>0.410531</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>-0.159938</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.410531</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>-0.222995</v>
       </c>
     </row>
     <row r="53">
@@ -5600,39 +5616,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Professional fees (Note 7)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2025 9,000,000 $ 524,573 $ 108,953 $</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>0.029802</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.030219</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0.372315</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>-0.261211</v>
       </c>
     </row>
     <row r="54">
@@ -5643,28 +5655,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
+          <t>Balance, December 31, 2022 9,000,000 $ 524,573 $ 108,953 $</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
-        <v>0.071605</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.009826</v>
+        <v>0.473588</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.00577</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.473588</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>-0.159938</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5685,12 +5697,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
+          <t>Professional fees (Note 7)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5699,10 +5711,10 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-0.047916</v>
+        <v>0.029802</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.043902</v>
+        <v>0.030219</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -5723,25 +5735,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 9,000,000 $ 524,573 $ 108,953 $</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transfer agent</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.071605</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.521504</v>
+        <v>0.009826</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.112022</v>
+        <v>0.00577</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -5767,24 +5781,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Professional fees (note 7)</t>
+          <t>Operating expenses total</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0.020393</v>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.029802</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.047916</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.043902</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -5805,29 +5819,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
+          <t>Balance, December 31, 2021 9,000,000 $ 524,573 $ 108,953 $</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.521504</v>
+      </c>
+      <c r="G58" s="5" t="n">
         <v>-0.112022</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>-0.047916</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -5848,20 +5858,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>common shares outstanding –</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Professional fees (note 7)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
-        <v>3.509589</v>
+        <v>0.020393</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>9</v>
+        <v>0.029802</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -5887,24 +5901,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Net loss and comprehensive</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Balance, April 12, 2021 (incorporation) 1 $ - $ - $</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>-0.112022</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>-0.047916</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -5930,22 +5944,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>common shares outstanding –</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Share subscriptions 3,999,999 200,000 -</t>
+          <t>common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.509589</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5971,22 +5983,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>common shares outstanding –</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Share subscriptions - IPO (note 4) 5,000,000 500,000 -</t>
+          <t>* The Company was incorporated on April 12, 2021, accordingly, there is no period for direct comparison.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.112022</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>-0.138079</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -6012,19 +6022,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>$       $   $                                     Total</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Share issue cost (broker warrants) (note 4) - (37,348) 37,348</t>
+          <t>$       $   $                                     Total</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E63" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6055,17 +6063,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>$       $   $              April                                        Contributed                                                                                                                                                                                                                                                                                                                  comparison.      on</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Share issue cost cash (note 4) - (138,079) -</t>
+          <t>$       $   $              April                                        Contributed                                                                                                                                                                                                                                                                                                                  comparison.      on</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" s="5" t="n">
-        <v>-0.138079</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6096,22 +6106,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 4) - - 71,605</t>
+          <t>direct for Capital 200,000 500,000 (37,348) (138,079) 524,573</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>0.071604</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7e-06</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.524573</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -6137,24 +6145,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>period                                    incorporation       $       $   $                                     Share                                     no</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Net loss for the period - - -</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>-0.112022</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>-0.112022</v>
+          <t>period                                    incorporation       $       $   $                                     Share                                     no is from 1 - - -</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -6180,20 +6188,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 * 9,000,000 $ 524,573 $ 108,953 $</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
-        <v>0.521504</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>-0.112022</v>
+        <v>0.019767</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -6224,16 +6238,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share based compensation (note 4)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
-        <v>0.019767</v>
+        <v>0.071605</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6269,12 +6279,16 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Share based compensation (note 4)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
-        <v>0.071605</v>
+        <v>-0.112022</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6310,16 +6324,18 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
+          <t>Basic and diluted loss per share $</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>-0.112022</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6350,23 +6366,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares outstanding – basic and diluted (note 4)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" s="5" t="n">
+        <v>3.509589</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6397,17 +6407,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted (note 4)</t>
+          <t>Balance, April 12, 2021 1 $ - $ - $ - $</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>3.509589</v>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6438,19 +6450,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>(incorporation)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Balance, April 12, 2021 1 $ - $ - $ - $</t>
+          <t>Share subscriptions 3,999,999 200,000 - -</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E73" s="5" t="n">
+        <v>0.2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6486,12 +6496,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Share subscriptions 3,999,999 200,000 - -</t>
+          <t>Share subscriptions - IPO 5,000,000 500,000 - -</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" s="5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6527,12 +6537,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Share subscriptions - IPO 5,000,000 500,000 - -</t>
+          <t>(note</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="n">
-        <v>0.5</v>
+        <v>4e-06</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6568,12 +6578,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(note</t>
+          <t>Share issue cost (broker - (37,348) 37,348 -</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>4e-06</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6609,14 +6621,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Share issue cost (broker - (37,348) 37,348 -</t>
+          <t>warrants) (note</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E77" s="5" t="n">
+        <v>4e-06</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6652,12 +6662,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>warrants) (note</t>
+          <t>Share issue cost cash (note 4) - (138,079) - -</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" s="5" t="n">
-        <v>4e-06</v>
+        <v>-0.138079</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6693,12 +6703,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Share issue cost cash (note 4) - (138,079) - -</t>
+          <t>Share-based compensation - - 71,605 -</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>-0.138079</v>
+        <v>0.071605</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6734,12 +6744,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 71,605 -</t>
+          <t>Net loss for the period - - - (112,022)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="n">
-        <v>0.071605</v>
+        <v>-0.112022</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6775,12 +6785,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Net loss for the period - - - (112,022)</t>
+          <t>Balance, December 31, 2021 9,000,000 $ 524,573 $ 108,953 $ (112,022) $</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" s="5" t="n">
-        <v>-0.112022</v>
+        <v>0.521504</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6798,47 +6808,6 @@
         </is>
       </c>
       <c r="I81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>(incorporation)</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2021 9,000,000 $ 524,573 $ 108,953 $ (112,022) $</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>0.521504</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/TRV.P.xlsx
+++ b/output/pdf_financials_xlsx/TRV.P.xlsx
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005026</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.021912</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.011365</v>
       </c>
     </row>
     <row r="13">
@@ -1035,13 +1035,13 @@
         <v>-0.047916</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.038876</v>
+        <v>-0.043902</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.024181</v>
+        <v>-0.046093</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.038216</v>
+        <v>-0.049581</v>
       </c>
     </row>
     <row r="28">
@@ -1079,13 +1079,13 @@
         <v>-0.047916</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.038876</v>
+        <v>-0.043902</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.024181</v>
+        <v>-0.046093</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.038216</v>
+        <v>-0.049581</v>
       </c>
     </row>
     <row r="30">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.580101</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.549942</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.505035</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.489549</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.422226</v>
       </c>
     </row>
     <row r="35">
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.580101</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.549942</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.505035</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.489549</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.422226</v>
       </c>
     </row>
     <row r="37">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">

--- a/output/pdf_financials_xlsx/TRV.P.xlsx
+++ b/output/pdf_financials_xlsx/TRV.P.xlsx
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-5.2e-05</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>5.2e-05</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0</v>
@@ -4262,7 +4262,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
